--- a/output/graficos_dimensiones/comunal_d_env_a_2021_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:16</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_antofagasta.xlsx
@@ -36,12 +36,12 @@
     <t xml:space="preserve">Antofagasta</t>
   </si>
   <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tocopilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Taltal</t>
-  </si>
-  <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
@@ -51,12 +51,12 @@
     <t xml:space="preserve">Mejillones</t>
   </si>
   <si>
+    <t xml:space="preserve">Ollagüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Pedro de Atacama</t>
   </si>
   <si>
-    <t xml:space="preserve">Ollagüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sierra Gorda</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -496,13 +496,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2301</v>
+        <v>2104</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>90.25</v>
+        <v>97.18</v>
       </c>
     </row>
     <row r="3">
@@ -513,13 +513,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2104</v>
+        <v>2301</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>89.29</v>
+        <v>96.43</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>75.2</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>72.51</v>
+        <v>77.34</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>61.46</v>
+        <v>65.99</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +587,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>57.95</v>
+        <v>61.68</v>
       </c>
     </row>
     <row r="8">
@@ -598,13 +598,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>51.39</v>
+        <v>56.41</v>
       </c>
     </row>
     <row r="9">
@@ -615,13 +615,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>51.16</v>
+        <v>54.75</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34.84</v>
+        <v>36.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:10</t>
+    <t xml:space="preserve">2026-10-02 16:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:25</t>
+    <t xml:space="preserve">2026-10-05 16:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
